--- a/order_generation/PO_excel_template/EE-RB-1.32.1.xlsx
+++ b/order_generation/PO_excel_template/EE-RB-1.32.1.xlsx
@@ -1330,7 +1330,7 @@
     <row r="69" ht="17.25" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>宁波品秀美容科技有限公司</t>
+          <t>宁波集秀美容科技有限公司</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
